--- a/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9706_escuela-bas-oscar-encalada-yovanovich_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B734B214-A9A3-47B3-B5E0-E21A13B56AAE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F117C84-4FA1-4BB2-A61C-7659341EB7F2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{906F11BA-E230-4853-A232-6B1D5E957D1B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A759F4CB-92CC-4541-8219-1F2076E625D1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB752397-C21C-4C61-830A-44B1F254F92C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E1B89F3-D636-4348-AF81-E22E9C5E81E4}"/>
 </file>